--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core CodeSystem Mode Validation Identite</t>
+    <t>FR Core CodeSystem Method Collection</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -150,16 +150,25 @@
     <t>Saisie manuelle</t>
   </si>
   <si>
+    <t>Saisie manuelle des traits d'identité, sans lecture de la carte Vitale ni interrogation du téléservice INSi (RNIV §4.3.3).</t>
+  </si>
+  <si>
     <t>CV</t>
   </si>
   <si>
-    <t>Carte vitale</t>
+    <t>Carte Vitale</t>
+  </si>
+  <si>
+    <t>Lecture de la carte Vitale physique de l'usager, permettant l'interrogation du téléservice INSi par ce canal (RNIV §4.3.2).</t>
   </si>
   <si>
     <t>INSI</t>
   </si>
   <si>
-    <t>Téléservice INSI</t>
+    <t>Téléservice INSi</t>
+  </si>
+  <si>
+    <t>Interrogation directe du téléservice INSi par saisie des traits d'identité, sans lecture de la carte Vitale (RNIV §4.3.3).</t>
   </si>
   <si>
     <t>CB</t>
@@ -168,10 +177,25 @@
     <t>Code à barre</t>
   </si>
   <si>
+    <t>Import de l'identité par scan du Datamatrix INS figurant sur un document de santé déjà porteur d'une identité qualifiée (Guide d'implémentation INS, EXI REC 02).</t>
+  </si>
+  <si>
     <t>RFID</t>
   </si>
   <si>
     <t>Puce RFID</t>
+  </si>
+  <si>
+    <t>Lecture d'une puce RFID (ex. bracelet patient) ; canal local de traçabilité, non défini par le RNIV.</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>Application carte Vitale</t>
+  </si>
+  <si>
+    <t>Obtention directe de l'INS par scan du QR code ou lecture NFC de l'Application carte Vitale (RNIV §4.3.4) ; l'identité ainsi obtenue est considérée comme qualifiée.</t>
   </si>
 </sst>
 </file>
@@ -489,7 +513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -517,7 +541,7 @@
         <v>44</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -525,13 +549,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -539,13 +563,13 @@
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +577,13 @@
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -567,13 +591,27 @@
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -150,7 +150,7 @@
     <t>Saisie manuelle</t>
   </si>
   <si>
-    <t>Saisie manuelle des traits d'identité, sans lecture de la carte Vitale ni interrogation du téléservice INSi (RNIV §4.3.3).</t>
+    <t>Saisie manuelle des traits d'identité, sans lecture de la carte Vitale ni interrogation du téléservice INSi.</t>
   </si>
   <si>
     <t>CV</t>
@@ -159,7 +159,7 @@
     <t>Carte Vitale</t>
   </si>
   <si>
-    <t>Lecture de la carte Vitale physique de l'usager, permettant l'interrogation du téléservice INSi par ce canal (RNIV §4.3.2).</t>
+    <t>Lecture de la carte Vitale physique de l'usager, permettant l'interrogation du téléservice INSi par ce canal.</t>
   </si>
   <si>
     <t>INSI</t>
@@ -168,7 +168,7 @@
     <t>Téléservice INSi</t>
   </si>
   <si>
-    <t>Interrogation directe du téléservice INSi par saisie des traits d'identité, sans lecture de la carte Vitale (RNIV §4.3.3).</t>
+    <t>Interrogation directe du téléservice INSi par saisie des traits d'identité, sans lecture de la carte Vitale.</t>
   </si>
   <si>
     <t>CB</t>
@@ -177,7 +177,7 @@
     <t>Code à barre</t>
   </si>
   <si>
-    <t>Import de l'identité par scan du Datamatrix INS figurant sur un document de santé déjà porteur d'une identité qualifiée (Guide d'implémentation INS, EXI REC 02).</t>
+    <t>Import de l'identité par scan du Datamatrix INS figurant sur un document de santé déjà porteur d'une identité qualifiée.</t>
   </si>
   <si>
     <t>RFID</t>
@@ -195,7 +195,7 @@
     <t>Application carte Vitale</t>
   </si>
   <si>
-    <t>Obtention directe de l'INS par scan du QR code ou lecture NFC de l'Application carte Vitale (RNIV §4.3.4) ; l'identité ainsi obtenue est considérée comme qualifiée.</t>
+    <t>Obtention directe de l'INS par scan du QR code ou lecture NFC de l'Application carte Vitale ; l'identité ainsi obtenue est considérée comme qualifiée.</t>
   </si>
 </sst>
 </file>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -186,7 +186,7 @@
     <t>Puce RFID</t>
   </si>
   <si>
-    <t>Lecture d'une puce RFID (ex. bracelet patient) ; canal local de traçabilité, non défini par le RNIV.</t>
+    <t>Lecture d'une puce RFID (ex. bracelet patient)</t>
   </si>
   <si>
     <t>AV</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
